--- a/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
+++ b/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>422 tests : 358 OK, 64 en échec</t>
+          <t>422 tests : 364 OK, 58 en échec</t>
         </is>
       </c>
     </row>
@@ -641,10 +641,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1041,10 +1041,10 @@
         <v>282</v>
       </c>
       <c r="C33" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D33" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -1173,16 +1173,6 @@
       </c>
       <c r="B44" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Défaut ouvert</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282 tests, 238 OK, 44 en échec</t>
+          <t>282 tests, 243 OK, 39 en échec</t>
         </is>
       </c>
     </row>
@@ -4974,27 +4964,19 @@
           <t>retours/test-connexion-bouton-pointage.js</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
-        </is>
-      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>10 / 10</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -9458,27 +9440,19 @@
           <t>retours/test-rh-badge-carte-par-page.js</t>
         </is>
       </c>
-      <c r="B241" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C241" s="5" t="inlineStr"/>
-      <c r="D241" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E241" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
-        </is>
-      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>6 / 6</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr"/>
+      <c r="E241" s="5" t="inlineStr"/>
+      <c r="F241" s="5" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -9486,27 +9460,19 @@
           <t>retours/test-rh-badge-qr.js</t>
         </is>
       </c>
-      <c r="B242" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C242" s="5" t="inlineStr"/>
-      <c r="D242" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E242" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
-        </is>
-      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>15 / 15</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr"/>
+      <c r="E242" s="5" t="inlineStr"/>
+      <c r="F242" s="5" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -9519,7 +9485,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr"/>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>14 / 14</t>
+        </is>
+      </c>
       <c r="D243" s="5" t="inlineStr"/>
       <c r="E243" s="5" t="inlineStr"/>
       <c r="F243" s="5" t="inlineStr"/>
@@ -9570,31 +9540,19 @@
           <t>retours/test-rh.js</t>
         </is>
       </c>
-      <c r="B246" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>48 / 49</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="inlineStr">
-        <is>
-          <t>Utilisateurs actifs créés et rattachés comme employés à l'ouverture (hors admin)  [1]</t>
-        </is>
-      </c>
-      <c r="E246" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
-        </is>
-      </c>
+          <t>49 / 49</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr"/>
+      <c r="E246" s="5" t="inlineStr"/>
+      <c r="F246" s="5" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -10362,27 +10320,19 @@
           <t>retours/test-whatsapp-session-alerte.js</t>
         </is>
       </c>
-      <c r="B282" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C282" s="5" t="inlineStr"/>
-      <c r="D282" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E282" s="5" t="inlineStr">
-        <is>
-          <t>Configuration du poste</t>
-        </is>
-      </c>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>Service WhatsApp Web non installé sur le poste.</t>
-        </is>
-      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>12 / 12</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr"/>
+      <c r="E282" s="5" t="inlineStr"/>
+      <c r="F282" s="5" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
@@ -11638,7 +11588,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14 tests, 13 OK, 1 en échec</t>
+          <t>14 tests, 14 OK, 0 en échec</t>
         </is>
       </c>
     </row>
@@ -11780,31 +11730,19 @@
           <t>audits/repro-vente-assurance.js</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>16 / 17</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>CR-04 attendu : 3 paires de clôtures simultanées sur le même organisme → encours = somme des parts  [clôtures réussies 6/6 ; somme des parts 3384 ; encours organisme 1692 ; encours client 1692]</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Défaut ouvert</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>CR-04 : deux clôtures simultanées sur le même organisme écrasent l'encours (lecture puis écriture en Java). Correction proposée : addition faite par la base, en une requête.</t>
-        </is>
-      </c>
+          <t>17 / 17</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -11937,11 +11875,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>10 / 10</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>

--- a/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
+++ b/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>422 tests : 364 OK, 58 en échec</t>
+          <t>422 tests : 352 OK, 70 en échec</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -641,10 +641,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -673,10 +673,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -865,10 +865,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +977,10 @@
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1041,10 +1041,10 @@
         <v>282</v>
       </c>
       <c r="C33" t="n">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D33" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -1057,10 +1057,10 @@
         <v>13</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1132,37 +1132,37 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Configuration du poste</t>
+          <t>Données de la copie</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Données de la copie</t>
+          <t>Lenteur (grosse base)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lenteur (grosse base)</t>
+          <t>Configuration du poste</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -2149,7 +2149,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12 tests, 11 OK, 1 en échec</t>
+          <t>12 tests, 9 OK, 3 en échec</t>
         </is>
       </c>
     </row>
@@ -2211,17 +2211,21 @@
           <t>journal/test-export-journal.js</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>10 / 10</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
+          <t>3 / 6</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>le bouton declenche bien un telechargement  [aucun]</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
     </row>
@@ -2291,17 +2295,21 @@
           <t>journal/test-scan-qr-publicitaire.js</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>13 / 13</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
+          <t>11 / 13</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Vente dépôt : lien scanné → aucun appel au serveur, « QR code publicitaire » sans fenêtre, champ vidé  [{"champ":"htt","fenetre":false,"texte":false} appels : ]</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
     </row>
@@ -2879,7 +2887,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>v1/checkproduit (tout) : réponse en moins de 20 s  [50990 ms, 11650]</t>
+          <t>v1/checkproduit (tout) : réponse en moins de 20 s  [58625 ms, 11650]</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -3003,12 +3011,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2 / 3</t>
+          <t>1 / 3</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Réponse 200 en moins de 30 s, un produit par article (193 articles détail sans indicateur)  [200, 120670 ms, 22112 / 22112]</t>
+          <t>Réponse 200 en moins de 30 s, un produit par article (193 articles détail sans indicateur)  [200, 133642 ms, 22112 / 22112]</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3557,7 +3565,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6 tests, 6 OK, 0 en échec</t>
+          <t>6 tests, 4 OK, 2 en échec</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3607,21 @@
           <t>productivite/test-activite-equipes-analyses.js</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>11 / 11</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
+          <t>10 / 11</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Parcours sans exception  [page.fill: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
@@ -3619,17 +3631,21 @@
           <t>productivite/test-activite-equipes-donnees.js</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>11 / 11</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
+          <t>0 / 1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Parcours sans exception  [locator.click: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
     </row>
@@ -4298,7 +4314,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282 tests, 243 OK, 39 en échec</t>
+          <t>282 tests, 233 OK, 49 en échec</t>
         </is>
       </c>
     </row>
@@ -4836,17 +4852,21 @@
           <t>retours/test-commande-en-cours-0825.js</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>5 / 5</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>1 / 2</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Parcours sans exception  [locator.click: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
     </row>
@@ -4924,17 +4944,21 @@
           <t>retours/test-connexion-badge-lecture.js</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>11 / 11</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr"/>
+          <t>8 / 10</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>QWERTY et verrouillage majuscules (« PRESTIGE°BQDGE*1*WWL°2… ») : connexion par le bouton badge  [http://localhost:8080/prestige/security/index.html]</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
     </row>
@@ -5328,17 +5352,21 @@
           <t>retours/test-differes-modification.js</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>13 / 13</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr"/>
+          <t>12 / 12</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>arrêt du test (code 1) sans contrôle en échec</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr"/>
     </row>
@@ -5628,17 +5656,21 @@
           <t>retours/test-etiquettes-gs1.js</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>17 / 17</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr"/>
+          <t>1 / 3</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="5" t="inlineStr"/>
     </row>
@@ -5648,17 +5680,21 @@
           <t>retours/test-etiquettes-personnalisation.js</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>50 / 50</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr"/>
+          <t>1 / 2</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="5" t="inlineStr"/>
     </row>
@@ -5912,17 +5948,21 @@
           <t>retours/test-fidelite-vente-utiliser.js</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>12 / 12</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr"/>
+          <t>11 / 11</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>arrêt du test (code 1) sans contrôle en échec</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="5" t="inlineStr"/>
     </row>
@@ -6020,17 +6060,21 @@
           <t>retours/test-gs1-bascule.js</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>25 / 25</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr"/>
+          <t>2 / 4</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr"/>
     </row>
@@ -6040,17 +6084,21 @@
           <t>retours/test-gs1-controle-lot.js</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>25 / 25</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr"/>
+          <t>2 / 4</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
     </row>
@@ -6424,17 +6472,21 @@
           <t>retours/test-journal-complet.js</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>18 / 18</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr"/>
+          <t>1 / 3</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
     </row>
@@ -6551,12 +6603,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>2 / 3</t>
+          <t>13 / 15</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Déroulement du test  [page.evaluate: Target crashed</t>
+          <t>(g) 10 erreurs identiques simultanées : un seul événement, 10 occurrences (aucune perdue)  [0|0]</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -6748,17 +6800,21 @@
           <t>retours/test-lot-l.js</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>31 / 31</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr"/>
+          <t>30 / 31</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>jeu d essai pose sur une fenetre vierge (2023-10-01 .. 2023-11-30)  [mouvements preexistants=10]</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="5" t="inlineStr"/>
     </row>
@@ -6773,7 +6829,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr"/>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>24 / 24</t>
+        </is>
+      </c>
       <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="5" t="inlineStr"/>
@@ -7268,7 +7328,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Avec le jeton : profil, droit photos, pas de pointage sans employé  [{"utilisateur":{"id":"90000000000000000001","login":"e2e","nom":"Essai E2E"},"employe":{"matricule":"e2e","id":"d3fe3b44-2f0a-4aaa-a272-ef7465d4a322","nom":"Essai E2E"},"success":true,"pointage":{"qr":true,"gps":false},"droits":{"pointage":true,"photos":true}}]</t>
+          <t>Avec le jeton : profil, droit photos, pas de pointage sans employé  [{"utilisateur":{"id":"90000000000000000001","login":"e2e","nom":"Essai E2E"},"employe":{"matricule":"E2E-BL-M1","id":"E2E-BL-1","nom":"ESSAI Badge lecture"},"success":true,"pointage":{"qr":true,"gps":false},"droits":{"pointage":true,"photos":true}}]</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -7524,7 +7584,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Elle porte la traçabilité : la saisie, sa date et son auteur  [s) (SIROP NON TENU) (1) () (5 ml le soir) (10 jours) (POMMADE PRESCRITE) (3) () (application locale) (15 jours) (TOTAL : 3 produit\(s\) prescrit\(s\)) (OBSERVATIONS) (Contrôle dans trois mois. Surveiller la tension.) (Saisie le 30/10/2026 07:43 par Essai E2E) (RC N° CI-TDI-2022-B-1010 - CC N° 2245364C - Centre des Impôts: YAMO]</t>
+          <t>Elle porte la traçabilité : la saisie, sa date et son auteur  [s) (SIROP NON TENU) (1) () (5 ml le soir) (10 jours) (POMMADE PRESCRITE) (3) () (application locale) (15 jours) (TOTAL : 3 produit\(s\) prescrit\(s\)) (OBSERVATIONS) (Contrôle dans trois mois. Surveiller la tension.) (Saisie le 30/10/2026 12:38 par Essai E2E) (RC N° CI-TDI-2022-B-1010 - CC N° 2245364C - Centre des Impôts: YAMO]</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -7716,7 +7776,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Le parcours va au bout  [Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-30283.cnf --default-character-set=utf8mb4 laborex_v1_db -e INSERT INTO t_famille_dci (lg_FAMILLE_DCI_ID, lg_FAMILLE_ID, lg_DCI_ID, str_STATUT, dt_CREATED, dt_UPDATED) SELECT CONCAT('E2E-SUB-', 0), f.lg_FAMILLE_ID,</t>
+          <t xml:space="preserve">Le parcours va au bout  [Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -e INSERT INTO t_famille_dci (lg_FAMILLE_DCI_ID, lg_FAMILLE_ID, lg_DCI_ID, str_STATUT, dt_CREATED, dt_UPDATED) SELECT CONCAT('E2E-SUB-', 0), f.lg_FAMILLE_ID, </t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -7756,17 +7816,17 @@
           <t>retours/test-paiement-points.js</t>
         </is>
       </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>25 / 25</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr"/>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr"/>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>arrêt du test (code 1) sans contrôle en échec</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="inlineStr"/>
       <c r="F163" s="5" t="inlineStr"/>
     </row>
@@ -8012,7 +8072,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Envoi (écran) : « a bien reçu la commande », pas d'échec ; en-tête de contrôle correct  [Envoi PharmaMLDPCI a bien reçu la commande. Sa réponse (quantités livrées, ruptures) n'est pas immédiate : elle sera récupérée automatiquement, ou par le bouton « Réponses PharmaML ». Ne renvoyez pas la commande.  OKOuiNonAnnuler[{"nature":"REQ_EMISSION","action":"COMMANDE","ref":"20261030074514","enRep":"","c</t>
+          <t>Envoi (écran) : « a bien reçu la commande », pas d'échec ; en-tête de contrôle correct  [Envoi PharmaMLDPCI a bien reçu la commande. Sa réponse (quantités livrées, ruptures) n'est pas immédiate : elle sera récupérée automatiquement, ou par le bouton « Réponses PharmaML ». Ne renvoyez pas la commande.  OKOuiNonAnnuler[{"nature":"REQ_EMISSION","action":"COMMANDE","ref":"20261030124508","enRep":"","c</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -8576,7 +8636,7 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Le parcours va au bout  [Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-30283.cnf --default-character-set=utf8mb4 laborex_v1_db -e INSERT INTO t_famille_dci (lg_FAMILLE_DCI_ID, lg_FAMILLE_ID, lg_DCI_ID, str_STATUT, dt_CREATED, dt_UPDATED) SELECT 'E2E-EQV-0', f.lg_FAMILLE_ID, '', 'enab</t>
+          <t>Le parcours va au bout  [Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -e INSERT INTO t_famille_dci (lg_FAMILLE_DCI_ID, lg_FAMILLE_ID, lg_DCI_ID, str_STATUT, dt_CREATED, dt_UPDATED) SELECT 'E2E-EQV-0', f.lg_FAMILLE_ID, '', 'enabl</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -8708,31 +8768,19 @@
           <t>retours/test-prevente.js</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>9 / 9</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 124) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>Lenteur (grosse base)</t>
-        </is>
-      </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>Dépasse 15 minutes sur la grosse base.</t>
-        </is>
-      </c>
+          <t>16 / 16</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr"/>
+      <c r="E207" s="5" t="inlineStr"/>
+      <c r="F207" s="5" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -8937,7 +8985,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr"/>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>15 / 15</t>
+        </is>
+      </c>
       <c r="D217" s="5" t="inlineStr"/>
       <c r="E217" s="5" t="inlineStr"/>
       <c r="F217" s="5" t="inlineStr"/>
@@ -9612,7 +9664,7 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>aucune lecture ne dépasse 30 s  [LotRessource.java GET v1/lot/lots [vide] 30003 ms : apiRequestContext.get: Timeout 30000ms exceeded.]</t>
+          <t>aucune lecture ne dépasse 30 s  [LotRessource.java GET v1/lot/lots [vide] 30008 ms : apiRequestContext.get: Timeout 30000ms exceeded.]</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
@@ -9644,7 +9696,7 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>aucune nouvelle erreur au Centre de support  [JAVA Blocage détecté : requête en traitement depuis 26s : POST /prestige/api/v1/vente (POST /prestige/api/v1/vente/ticket/vno)]</t>
+          <t>aucune nouvelle erreur au Centre de support  [JAVA Blocage détecté : requête en traitement depuis 26s : GET /prestige/api/v1/fichea (GET /prestige/api/v1/fichearticle/comparaison/excel)]</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
@@ -10240,17 +10292,21 @@
           <t>retours/test-ventes-terminees-colonnes.js</t>
         </is>
       </c>
-      <c r="B278" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>14 / 14</t>
-        </is>
-      </c>
-      <c r="D278" s="5" t="inlineStr"/>
+          <t>13 / 14</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>Colonne « P » : vente sans poste connu → vide, encaissement dans l'infobulle  [{"texte":"RM","qtip":"Saisie : RM&lt;br&gt;Encaissement : RM"}]</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="inlineStr"/>
       <c r="F278" s="5" t="inlineStr"/>
     </row>
@@ -10360,27 +10416,19 @@
           <t>retours/test-whatsapp-web.js</t>
         </is>
       </c>
-      <c r="B284" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C284" s="5" t="inlineStr"/>
-      <c r="D284" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E284" s="5" t="inlineStr">
-        <is>
-          <t>Configuration du poste</t>
-        </is>
-      </c>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>Service WhatsApp Web (outils/whatsapp-web) non installé sur le poste.</t>
-        </is>
-      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>16 / 16</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr"/>
+      <c r="E284" s="5" t="inlineStr"/>
+      <c r="F284" s="5" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
@@ -10395,7 +10443,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>16 / 25</t>
+          <t>17 / 26</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -10447,7 +10495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13 tests, 11 OK, 2 en échec</t>
+          <t>13 tests, 12 OK, 1 en échec</t>
         </is>
       </c>
     </row>
@@ -10629,31 +10677,19 @@
           <t>securite/test-horloge.js</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2 / 5</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Précondition : horloge du serveur juste, fuseau attendu (Africa/Abidjan), heure d'Internet joignable  [{"fuseau":"Etc/UTC","reference":null,"anomalies":[]}]</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Configuration du poste</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Serveur en UTC alors que le test attend Africa/Abidjan (même heure) et un accès à l'heure d'Internet.</t>
-        </is>
-      </c>
+          <t>11 / 11</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -10748,12 +10784,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2 / 3</t>
+          <t>4 / 5</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Parcours sans exception  [page.click: Timeout 30000ms exceeded.</t>
+          <t>« Terminer la vente » : vente en dépôt terminée par admin, aucun refus du serveur  [is_Closed|e2e | réponses 200 | Impression du ticketVoulez-vous imprimer le ticket ?OKOuiNonAnnuler]</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11183,7 +11219,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Onglet Expérience utilisateur : courbe, par poste, écrans et appels les plus lents  [{"serie":20,"postes":1,"ecrans":["RapportGestions","comparaisonChiffreAffaireManager","statfamilleartcl","analysearticle","analyseFrequentationOffManager","articlevendurecapitulatif","activitiessummary","pointagebl","pilotage","mouvementprixvente","statistiqueuniteventemanager","pososmanager","analy]</t>
+          <t>Onglet Expérience utilisateur : courbe, par poste, écrans et appels les plus lents  [{"serie":24,"postes":1,"ecrans":["RapportGestions","comparaisonChiffreAffaireManager","statfamilleartcl","articlevendurecapitulatif","analysearticle","analyseFrequentationOffManager","mouvementprixvente","activitiessummary","pilotage","statistiqueuniteventemanager","analysetierspayant","gestioncaiss]</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11459,7 +11495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3 tests, 3 OK, 0 en échec</t>
+          <t>3 tests, 2 OK, 1 en échec</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11537,21 @@
           <t>audit/test-audit-analyse.js</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>17 / 17</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
+          <t>16 / 17</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Analyse à l'ouverture en moins de 10 s avec 300 clients en différé et 7200 règlements  [{"ms":11040}]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
@@ -11588,7 +11628,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14 tests, 14 OK, 0 en échec</t>
+          <t>14 tests, 13 OK, 1 en échec</t>
         </is>
       </c>
     </row>
@@ -11850,17 +11890,21 @@
           <t>audits/test-ecran-modifier-vente-deja-modifiee.js</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Échec</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>6 / 6</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
+          <t>1 / 3</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Préparation : vente modifiée, copie clôturée  [ {"s":false}]</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
     </row>
@@ -11875,7 +11919,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>10 / 10</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
@@ -12042,7 +12090,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8 tests, 4 OK, 4 en échec</t>
+          <t>8 tests, 7 OK, 1 en échec</t>
         </is>
       </c>
     </row>
@@ -12084,27 +12132,19 @@
           <t>campagnes/test-campagne-piece-jointe.js</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Configuration du poste</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Service WhatsApp Web non installé sur le poste.</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>21 / 21</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -12132,31 +12172,19 @@
           <t>campagnes/test-campagnes-destinataires-demande.js</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>3 / 4</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Parcours sans exception  [page.waitForFunction: Timeout 60000ms exceeded.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
-        </is>
-      </c>
+          <t>5 / 5</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -12231,7 +12259,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>8 / 15</t>
+          <t>21 / 27</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -12256,31 +12284,19 @@
           <t>campagnes/test-whatsapp-discussions.js</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>3 / 4</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Parcours sans exception  [locator.click: Timeout 30000ms exceeded.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
-        </is>
-      </c>
+          <t>15 / 15</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
+++ b/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>422 tests : 352 OK, 70 en échec</t>
+          <t>422 tests : 366 OK, 56 en échec</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -641,10 +641,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -865,10 +865,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +977,10 @@
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1041,10 +1041,10 @@
         <v>282</v>
       </c>
       <c r="C33" t="n">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D33" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
@@ -1168,10 +1168,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Données d'essai</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Test manuel</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2149,7 +2159,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12 tests, 9 OK, 3 en échec</t>
+          <t>12 tests, 10 OK, 2 en échec</t>
         </is>
       </c>
     </row>
@@ -2211,21 +2221,17 @@
           <t>journal/test-export-journal.js</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>3 / 6</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>le bouton declenche bien un telechargement  [aucun]</t>
-        </is>
-      </c>
+          <t>10 / 10</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
     </row>
@@ -2310,8 +2316,16 @@
           <t>Vente dépôt : lien scanné → aucun appel au serveur, « QR code publicitaire » sans fenêtre, champ vidé  [{"champ":"htt","fenetre":false,"texte":false} appels : ]</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>À examiner</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Partie « vente dépôt » en échec deux fois de suite l'après-midi (champ partiellement saisi) ; passait le matin.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3565,7 +3579,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6 tests, 4 OK, 2 en échec</t>
+          <t>6 tests, 6 OK, 0 en échec</t>
         </is>
       </c>
     </row>
@@ -3607,21 +3621,17 @@
           <t>productivite/test-activite-equipes-analyses.js</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>10 / 11</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Parcours sans exception  [page.fill: Timeout 30000ms exceeded.</t>
-        </is>
-      </c>
+          <t>11 / 11</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
@@ -3631,21 +3641,17 @@
           <t>productivite/test-activite-equipes-donnees.js</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>0 / 1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Parcours sans exception  [locator.click: Timeout 30000ms exceeded.</t>
-        </is>
-      </c>
+          <t>11 / 11</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
     </row>
@@ -4314,7 +4320,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282 tests, 233 OK, 49 en échec</t>
+          <t>282 tests, 242 OK, 40 en échec</t>
         </is>
       </c>
     </row>
@@ -4852,21 +4858,17 @@
           <t>retours/test-commande-en-cours-0825.js</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>1 / 2</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Parcours sans exception  [locator.click: Timeout 30000ms exceeded.</t>
-        </is>
-      </c>
+          <t>5 / 5</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
     </row>
@@ -4944,21 +4946,17 @@
           <t>retours/test-connexion-badge-lecture.js</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>8 / 10</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>QWERTY et verrouillage majuscules (« PRESTIGE°BQDGE*1*WWL°2… ») : connexion par le bouton badge  [http://localhost:8080/prestige/security/index.html]</t>
-        </is>
-      </c>
+          <t>11 / 11</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
     </row>
@@ -5357,18 +5355,22 @@
           <t>Échec</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>12 / 12</t>
-        </is>
-      </c>
+      <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
           <t>arrêt du test (code 1) sans contrôle en échec</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Données d'essai</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Clients d'essai restés en base après l'arrêt des serveurs à 11 h 07 (le test ne peut pas recréer son jeu d'essai) ; passait le matin. À rejouer après nettoyage.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5656,21 +5658,17 @@
           <t>retours/test-etiquettes-gs1.js</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>1 / 3</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
-        </is>
-      </c>
+          <t>17 / 17</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="5" t="inlineStr"/>
     </row>
@@ -5680,21 +5678,17 @@
           <t>retours/test-etiquettes-personnalisation.js</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>1 / 2</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
-        </is>
-      </c>
+          <t>50 / 50</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr"/>
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="5" t="inlineStr"/>
     </row>
@@ -5953,18 +5947,22 @@
           <t>Échec</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>11 / 11</t>
-        </is>
-      </c>
+      <c r="C77" s="5" t="inlineStr"/>
       <c r="D77" s="5" t="inlineStr">
         <is>
           <t>arrêt du test (code 1) sans contrôle en échec</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Données d'essai</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Clients d'essai restés en base après l'arrêt des serveurs à 11 h 07 (le test ne peut pas recréer son jeu d'essai) ; passait le matin. À rejouer après nettoyage.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -6060,21 +6058,17 @@
           <t>retours/test-gs1-bascule.js</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>2 / 4</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
-        </is>
-      </c>
+          <t>25 / 25</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr"/>
     </row>
@@ -6084,21 +6078,17 @@
           <t>retours/test-gs1-controle-lot.js</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2 / 4</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
-        </is>
-      </c>
+          <t>25 / 25</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr"/>
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
     </row>
@@ -6472,21 +6462,17 @@
           <t>retours/test-journal-complet.js</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>1 / 3</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>Déroulement du test  [Error: Command failed: mariadb --defaults-extra-file=C:/Users/AIRMAN/AppData/Local/Temp/claude/D--projet-p3-prestige/4660ea01-cd8f-49ab-bd78-f6382d44836c/scratchpad/e2e-1776.cnf --default-character-set=utf8mb4 laborex_v1_db -sN</t>
-        </is>
-      </c>
+          <t>18 / 18</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr"/>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
     </row>
@@ -6800,21 +6786,17 @@
           <t>retours/test-lot-l.js</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>30 / 31</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>jeu d essai pose sur une fenetre vierge (2023-10-01 .. 2023-11-30)  [mouvements preexistants=10]</t>
-        </is>
-      </c>
+          <t>31 / 31</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="5" t="inlineStr"/>
     </row>
@@ -7827,8 +7809,16 @@
           <t>arrêt du test (code 1) sans contrôle en échec</t>
         </is>
       </c>
-      <c r="E163" s="5" t="inlineStr"/>
-      <c r="F163" s="5" t="inlineStr"/>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>Données d'essai</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Clients d'essai restés en base après l'arrêt des serveurs à 11 h 07 (le test ne peut pas recréer son jeu d'essai) ; passait le matin. À rejouer après nettoyage.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -10292,21 +10282,17 @@
           <t>retours/test-ventes-terminees-colonnes.js</t>
         </is>
       </c>
-      <c r="B278" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>13 / 14</t>
-        </is>
-      </c>
-      <c r="D278" s="5" t="inlineStr">
-        <is>
-          <t>Colonne « P » : vente sans poste connu → vide, encaissement dans l'infobulle  [{"texte":"RM","qtip":"Saisie : RM&lt;br&gt;Encaissement : RM"}]</t>
-        </is>
-      </c>
+          <t>14 / 14</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr"/>
       <c r="E278" s="5" t="inlineStr"/>
       <c r="F278" s="5" t="inlineStr"/>
     </row>
@@ -11495,7 +11481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3 tests, 2 OK, 1 en échec</t>
+          <t>3 tests, 3 OK, 0 en échec</t>
         </is>
       </c>
     </row>
@@ -11537,21 +11523,17 @@
           <t>audit/test-audit-analyse.js</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>16 / 17</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Analyse à l'ouverture en moins de 10 s avec 300 clients en différé et 7200 règlements  [{"ms":11040}]</t>
-        </is>
-      </c>
+          <t>17 / 17</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
     </row>
@@ -11628,7 +11610,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14 tests, 13 OK, 1 en échec</t>
+          <t>14 tests, 14 OK, 0 en échec</t>
         </is>
       </c>
     </row>
@@ -11890,21 +11872,17 @@
           <t>audits/test-ecran-modifier-vente-deja-modifiee.js</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>1 / 3</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Préparation : vente modifiée, copie clôturée  [ {"s":false}]</t>
-        </is>
-      </c>
+          <t>6 / 6</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
     </row>

--- a/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
+++ b/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>422 tests : 366 OK, 56 en échec</t>
+          <t>422 tests : 369 OK, 53 en échec</t>
         </is>
       </c>
     </row>
@@ -1041,10 +1041,10 @@
         <v>282</v>
       </c>
       <c r="C33" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
@@ -1168,20 +1168,10 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Données d'essai</t>
+          <t>Test manuel</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Test manuel</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4320,7 +4310,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282 tests, 242 OK, 40 en échec</t>
+          <t>282 tests, 245 OK, 37 en échec</t>
         </is>
       </c>
     </row>
@@ -5350,27 +5340,19 @@
           <t>retours/test-differes-modification.js</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Données d'essai</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Clients d'essai restés en base après l'arrêt des serveurs à 11 h 07 (le test ne peut pas recréer son jeu d'essai) ; passait le matin. À rejouer après nettoyage.</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>13 / 13</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5942,27 +5924,19 @@
           <t>retours/test-fidelite-vente-utiliser.js</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Données d'essai</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Clients d'essai restés en base après l'arrêt des serveurs à 11 h 07 (le test ne peut pas recréer son jeu d'essai) ; passait le matin. À rejouer après nettoyage.</t>
-        </is>
-      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>12 / 12</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -7798,27 +7772,19 @@
           <t>retours/test-paiement-points.js</t>
         </is>
       </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr"/>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>Données d'essai</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>Clients d'essai restés en base après l'arrêt des serveurs à 11 h 07 (le test ne peut pas recréer son jeu d'essai) ; passait le matin. À rejouer après nettoyage.</t>
-        </is>
-      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>25 / 25</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr"/>
+      <c r="E163" s="5" t="inlineStr"/>
+      <c r="F163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">

--- a/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
+++ b/docs/recette/RAPPORT_TESTS_ECRAN_2026-10-30.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>422 tests : 369 OK, 53 en échec</t>
+          <t>422 tests : 370 OK, 52 en échec</t>
         </is>
       </c>
     </row>
@@ -865,10 +865,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
@@ -2149,7 +2149,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12 tests, 10 OK, 2 en échec</t>
+          <t>12 tests, 11 OK, 1 en échec</t>
         </is>
       </c>
     </row>
@@ -2291,31 +2291,19 @@
           <t>journal/test-scan-qr-publicitaire.js</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>11 / 13</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Vente dépôt : lien scanné → aucun appel au serveur, « QR code publicitaire » sans fenêtre, champ vidé  [{"champ":"htt","fenetre":false,"texte":false} appels : ]</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>À examiner</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Partie « vente dépôt » en échec deux fois de suite l'après-midi (champ partiellement saisi) ; passait le matin.</t>
-        </is>
-      </c>
+          <t>13 / 13</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -5265,10 +5253,14 @@
           <t>Échec</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>57 / 59</t>
+        </is>
+      </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>arrêt du test (code 1) sans contrôle en échec</t>
+          <t>C est le fond de l onglet qui est coloré, et les quatre fonds sont différents  [["rgb(30, 58, 95)","rgb(255, 255, 255)","rgb(255, 255, 255)","rgb(255, 255, 255)"]]</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -5278,7 +5270,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Pas encore étudié : test à adapter à la copie ou défaut à confirmer.</t>
+          <t>Le test va maintenant au bout (57 / 59) : seules les couleurs des onglets diffèrent (fond coloré sur le seul onglet actif, libellé non blanc sur les autres). Avant, il échouait dès la pose du jeu d'essai (rayon vide) et laissait son dépôt dans la base.</t>
         </is>
       </c>
     </row>
